--- a/certificates-template.xlsx
+++ b/certificates-template.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\4JMwq%#9510#T@\موقع\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5532F573-0D19-46B3-98FF-D3BCFE048CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Certificates" sheetId="1" r:id="rId4"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId5"/>
+    <sheet name="Certificates" sheetId="1" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
   <si>
     <t>student_email</t>
   </si>
@@ -39,42 +44,9 @@
     <t>certificate_code</t>
   </si>
   <si>
-    <t>ahmed.ali@example.com</t>
-  </si>
-  <si>
-    <t>شهادة إتمام الدورة</t>
-  </si>
-  <si>
-    <t>2024-06-15</t>
-  </si>
-  <si>
     <t>ممتاز</t>
   </si>
   <si>
-    <t>INSEP-2024-001</t>
-  </si>
-  <si>
-    <t>fatima.hassan@example.com</t>
-  </si>
-  <si>
-    <t>2024-09-01</t>
-  </si>
-  <si>
-    <t>جيد جداً</t>
-  </si>
-  <si>
-    <t>INSEP-2024-002</t>
-  </si>
-  <si>
-    <t>omar.khalid@example.com</t>
-  </si>
-  <si>
-    <t>2024-11-20</t>
-  </si>
-  <si>
-    <t>sara.nasser@example.com</t>
-  </si>
-  <si>
     <t>Column</t>
   </si>
   <si>
@@ -127,70 +99,95 @@
   </si>
   <si>
     <t>• Rows with an unregistered email or invalid course_id will be skipped.</t>
+  </si>
+  <si>
+    <t>Omnya matarawy Mohammed Dhaifalla</t>
+  </si>
+  <si>
+    <t>Mohamed khedr sophy yousif</t>
+  </si>
+  <si>
+    <t>Hassan mahmoud mohamed helmy</t>
+  </si>
+  <si>
+    <t>Omnia Ashraf Saad Osman</t>
+  </si>
+  <si>
+    <t>Mohamed Ahmed Abdul Alim Abdel Motagally</t>
+  </si>
+  <si>
+    <t>Mohamed Yassen Atia Yassen</t>
+  </si>
+  <si>
+    <t>Salma samara ramadan Ibrahim</t>
+  </si>
+  <si>
+    <t>Ahmed Hesham AlـEmam Al-Maghlawy</t>
+  </si>
+  <si>
+    <t>Helana Gerges Youssef Yaqup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كورس التشريح الرياضي </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF1A3A5C"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF374151"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFDC2626"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,24 +202,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F4FF"/>
+        <fgColor rgb="FFF8FAFF"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EFF9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFF"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -245,38 +236,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="5" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="5" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="5" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="5" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -566,23 +583,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="true" style="0"/>
-    <col min="2" max="2" width="14" customWidth="true" style="0"/>
-    <col min="3" max="3" width="14" customWidth="true" style="0"/>
-    <col min="4" max="4" width="34" customWidth="true" style="0"/>
-    <col min="5" max="5" width="18" customWidth="true" style="0"/>
-    <col min="6" max="6" width="18" customWidth="true" style="0"/>
-    <col min="7" max="7" width="26" customWidth="true" style="0"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" customHeight="1" ht="22">
+    <row r="1" spans="1:7" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,241 +617,355 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="10">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3">
-        <v>3</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G2" s="10">
+        <v>100018361</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="10">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="10">
+        <v>100018362</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="10">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="10">
+        <v>100018363</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="10">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="10">
+        <v>100018364</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="10">
+        <v>1</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="10">
+        <v>100018365</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="10">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="10">
+        <v>100018366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="10">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="10">
+        <v>100018367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="10">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="10">
+        <v>100018368</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="10">
+        <v>100018369</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C12" s="10"/>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="true" style="0"/>
-    <col min="2" max="2" width="14" customWidth="true" style="0"/>
-    <col min="3" max="3" width="60" customWidth="true" style="0"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="6" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="8" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="10" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="10" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="5" t="s">
-        <v>36</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>